--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/Migration/BIBS_Migration_BRD-13_Data_Requirements_Workbook_v1.2.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/Migration/BIBS_Migration_BRD-13_Data_Requirements_Workbook_v1.2.xlsx
@@ -377,7 +377,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <font>
         <b val="1"/>
@@ -415,6 +415,18 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E5F5FF"/>
+          <bgColor rgb="00E5F5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00004EA8"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00E5F5FF"/>
@@ -31159,7 +31171,7 @@
       </c>
       <c r="N22" s="12" t="inlineStr">
         <is>
-          <t>One file in every mock; final file with the RAs sent up to T-5; resubmissions of corrected rows until T-1 12:00</t>
+          <t>One file in every trial migration; final file with the RAs sent up to T-5; resubmissions of corrected rows until T-1 12:00</t>
         </is>
       </c>
       <c r="O22" s="12" t="inlineStr">
@@ -31174,7 +31186,7 @@
       </c>
       <c r="Q22" s="12" t="inlineStr">
         <is>
-          <t>M4 (9 Apr 2027) (Mock 1); final at T-5</t>
+          <t>M4 (9 Apr 2027) (Trial migration 1); final at T-5</t>
         </is>
       </c>
       <c r="R22" s="12" t="n">
@@ -47593,7 +47605,7 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Number of mocks and the dress rehearsal; masked production extracts in SIT / UAT; who masks and approves</t>
+          <t>Number of trial migrations and the dress rehearsal; masked production extracts in SIT / UAT; who masks and approves</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
@@ -48036,9 +48048,12 @@
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"ANSWERED"</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="4" stopIfTrue="1">
+      <formula>"RECOMMENDED"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:I546">
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="5" dxfId="3">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48187,7 +48202,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Extracts for Mock 1 (SIT migration starts); reference data and clients first</t>
+          <t>Extracts for Trial migration 1 (SIT migration starts); reference data and clients first</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -48204,7 +48219,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Code maps approved for Mock 2 (G2), including the PACKAGE map</t>
+          <t>Code maps approved for Trial migration 2 (G2), including the PACKAGE map</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
